--- a/테이블/몬스터/몬스터 패턴 테이블.xlsx
+++ b/테이블/몬스터/몬스터 패턴 테이블.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\addmin\Desktop\Unreal\Project TirgerGhostField\기획\테이블\몬스터\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED9F6611-FD99-4A4B-9304-D2C19A16F17B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{252916A7-3B69-4930-8352-47E5CD8C6AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="도메인 정의" sheetId="1" r:id="rId1"/>
@@ -703,7 +703,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72C19B3A-9DE6-4959-8646-89E4535BEFF0}">
-  <dimension ref="B1:H1"/>
+  <dimension ref="B1:H10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="7.5" bestFit="1" customWidth="1"/>
@@ -745,6 +745,213 @@
         <v>빈도 수치</v>
       </c>
     </row>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B2">
+        <v>100</v>
+      </c>
+      <c r="C2">
+        <v>1000</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B3">
+        <v>101</v>
+      </c>
+      <c r="C3">
+        <v>1000</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>102</v>
+      </c>
+      <c r="C4">
+        <v>1000</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>103</v>
+      </c>
+      <c r="C5">
+        <v>1001</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>104</v>
+      </c>
+      <c r="C6">
+        <v>1001</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>105</v>
+      </c>
+      <c r="C7">
+        <v>1001</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>106</v>
+      </c>
+      <c r="C8">
+        <v>1002</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>8</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>3</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>107</v>
+      </c>
+      <c r="C9">
+        <v>1002</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+      <c r="F9">
+        <v>4</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+      <c r="H9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>108</v>
+      </c>
+      <c r="C10">
+        <v>1002</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>10</v>
+      </c>
+      <c r="F10">
+        <v>4</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
